--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7575" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1395,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="25.1428571428571" customWidth="1"/>
@@ -2204,20 +2204,343 @@
         <v>8</v>
       </c>
     </row>
+    <row r="48" hidden="1" spans="1:5">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:5">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:5">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:5">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="1:5">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="1:5">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" spans="1:5">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" spans="1:5">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" spans="1:5">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" spans="1:5">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" spans="1:5">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" t="s">
+        <v>115</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" spans="1:5">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" spans="1:5">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" hidden="1" spans="1:5">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" spans="1:5">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" spans="1:5">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" t="s">
+        <v>120</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" spans="1:5">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" t="s">
+        <v>121</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" spans="1:5">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" t="s">
+        <v>122</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="66" hidden="1" spans="1:5">
       <c r="A66" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" spans="1:5">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2226,13 +2549,13 @@
         <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
@@ -2243,13 +2566,13 @@
         <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
@@ -2260,13 +2583,13 @@
         <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C70" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -2277,347 +2600,24 @@
         <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:5">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C72" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" t="s">
-        <v>110</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" hidden="1" spans="1:5">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C73" t="s">
-        <v>111</v>
-      </c>
-      <c r="D73" t="s">
-        <v>111</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" hidden="1" spans="1:5">
-      <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>112</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" hidden="1" spans="1:5">
-      <c r="A75" t="s">
-        <v>9</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C75" t="s">
-        <v>113</v>
-      </c>
-      <c r="D75" t="s">
-        <v>113</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" hidden="1" spans="1:5">
-      <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C76" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
-        <v>114</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" hidden="1" spans="1:5">
-      <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C77" t="s">
-        <v>115</v>
-      </c>
-      <c r="D77" t="s">
-        <v>115</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" hidden="1" spans="1:5">
-      <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C78" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" t="s">
-        <v>116</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" hidden="1" spans="1:5">
-      <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" t="s">
-        <v>117</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" hidden="1" spans="1:5">
-      <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" t="s">
-        <v>118</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" hidden="1" spans="1:5">
-      <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" t="s">
-        <v>119</v>
-      </c>
-      <c r="D81" t="s">
-        <v>119</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" hidden="1" spans="1:5">
-      <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82" t="s">
-        <v>120</v>
-      </c>
-      <c r="D82" t="s">
-        <v>120</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" hidden="1" spans="1:5">
-      <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" t="s">
-        <v>121</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" hidden="1" spans="1:5">
-      <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C84" t="s">
-        <v>122</v>
-      </c>
-      <c r="D84" t="s">
-        <v>122</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" hidden="1" spans="1:5">
-      <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C85" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" t="s">
-        <v>123</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" hidden="1" spans="1:5">
-      <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C86" t="s">
-        <v>124</v>
-      </c>
-      <c r="D86" t="s">
-        <v>124</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" hidden="1" spans="1:5">
-      <c r="A87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>125</v>
-      </c>
-      <c r="D87" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" hidden="1" spans="1:5">
-      <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" t="s">
-        <v>126</v>
-      </c>
-      <c r="D88" t="s">
-        <v>127</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" spans="1:5">
-      <c r="A89" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" t="s">
-        <v>43</v>
-      </c>
-      <c r="D89" t="s">
-        <v>128</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" hidden="1" spans="1:5">
-      <c r="A90" t="s">
-        <v>9</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C90" t="s">
-        <v>129</v>
-      </c>
-      <c r="D90" t="s">
-        <v>129</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E90" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E71" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="fra"/>
-      </customFilters>
+      <filters>
+        <filter val="fra"/>
+      </filters>
     </filterColumn>
     <extLst/>
   </autoFilter>
